--- a/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
+++ b/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
@@ -1179,39 +1179,43 @@
       <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Огнезащитная изоляция</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>МБФ 5</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Огнезащита МБФ-5 (EI 30, EI 45)</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="10" t="n">
         <v>12411</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>komplektovik.ru</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>http://komplektovik.ru/vse-dlya-montaja/krepejnie-materialy/teploizoljacija-ognezashita-vozduhovodov-v-tolyatti/ognezaxhita-mbf-5-tolyatti-samara-kupit/</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>⚠ цена, похоже, за рулон, в позиции м² (104 м²)</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1860,39 +1864,43 @@
       <c r="I41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Термометр биметаллический O80мм 0..120С, L=100 мм, кл. точн. 1.5, IP54</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>IP54</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Общепромышленные биметаллические термометры ТБф-120 d.100</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="10" t="n">
         <v>870</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>www.fiztech.ru</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>https://www.fiztech.ru/catalog/termometry/537/</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>⚠ в позиции корпус Ø80, на карточке d.100</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2050,7 +2058,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Манометр М2 радиальный ТМ-510Р.00 0...1.0 МРа 1/2&amp;apos; кл.1.5., цвет-</t>
+          <t>Манометр М2 радиальный ТМ-510Р.00 0...1.0 МРа 1/2' кл.1.5., цвет-</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -2280,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2304,7 +2312,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Искали по 23 позициям с заводской маркой, цена нашлась у 14</t>
+          <t>Искали по 14 позициям с заводской маркой, цена нашлась у 14</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2554,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Редуктор давления поршневой Heizen 1/2&amp;amp;quot;</t>
+          <t>Редуктор давления поршневой Heizen 1/2"</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
@@ -2853,53 +2861,29 @@
       </c>
       <c r="I18" s="8" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Искали, но цену не нашли:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Спецификация элементов стояка К1.1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>К1.1</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Спецификация элементов узла воздухоотводчика на зону</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ОА-06-03-2024-ВК</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Заголовки узлов по проекту — отдельной цены у них нет:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Спецификация элементов стояков на этаж</t>
+          <t>Спецификация элементов стояка К1.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ОА-06-03-2024-ВК</t>
+          <t>К1.1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Спецификация элементов узла ввода в квартиру</t>
+          <t>Спецификация элементов узла воздухоотводчика на зону</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2911,7 +2895,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Спецификация элементов коллекторного узла офисных помещений</t>
+          <t>Спецификация элементов стояков на этаж</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2923,7 +2907,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Спецификация элементов коллекторного узла</t>
+          <t>Спецификация элементов узла ввода в квартиру</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2935,7 +2919,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Спецификация элементов коллекторного узла 3-12 этажей</t>
+          <t>Спецификация элементов коллекторного узла офисных помещений</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2947,7 +2931,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Спецификация элементов коллекторного узла 13-21 этажей</t>
+          <t>Спецификация элементов коллекторного узла</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2959,10 +2943,34 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
+          <t>Спецификация элементов коллекторного узла 3-12 этажей</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ОА-06-03-2024-ВК</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Спецификация элементов коллекторного узла 13-21 этажей</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ОА-06-03-2024-ВК</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Спецификация элементов коллекторного узла 22 и</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>ОА-06-03-2024-ВК</t>
         </is>

--- a/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
+++ b/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Искали по 53 позициям с заводской маркой, цена нашлась у 44</t>
+          <t>Искали по 53 позициям с заводской маркой, цена нашлась у 43</t>
         </is>
       </c>
     </row>
@@ -654,74 +654,82 @@
       <c r="I7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Compact</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>C22-400-1400</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Панельный радиатор Evra Compact (тип 22 высота 400 мм длина 1400 мм) б</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>11443</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>nord-heat.ru</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>https://nord-heat.ru/steel/compact/c22-400-1400.html</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Радиатор стальной панельный 22/400/1400 боковое подключение</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>42159</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>www.etm.ru</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>https://www.etm.ru/cat/nn/8158067</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>⚠ бренд не указан, цена в ~4 раза выше прошлой находки</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Compact</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>C33-400-1000</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Радиатор стальной панельный EVRA Compact 33-400-1000, подкл боковое, R</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>20745</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>www.termoros-spb.ru</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.termoros-spb.ru/catalog/pribory_otopleniya/radiatory/panelnye_stalnye/evra_compact_c/264783/</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Радиатор стальной панельный 33/400/1000 боковое подключение</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>45857</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>www.etm.ru</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>https://www.etm.ru/cat/nn/2168747</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>⚠ бренд не указан, цена в ~2 раза выше прошлой находки</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -944,16 +952,16 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>CV22-400-900</t>
+          <t>CV22-400-1000</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 900</t>
+          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 100</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>9692</v>
+        <v>10598</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -962,7 +970,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-900.html</t>
+          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1000.html</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
@@ -979,16 +987,16 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>CV22-400-1000</t>
+          <t>CV22-400-1200</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 100</t>
+          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 120</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>10598</v>
+        <v>11953</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -997,7 +1005,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1000.html</t>
+          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1200.html</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
@@ -1014,16 +1022,16 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>CV22-400-1200</t>
+          <t>CV22-400-1400</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 120</t>
+          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 140</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>11953</v>
+        <v>13277</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1032,7 +1040,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1200.html</t>
+          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1400.html</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
@@ -1049,16 +1057,16 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>CV22-400-1400</t>
+          <t>CV22-400-1600</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 140</t>
+          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 160</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>13277</v>
+        <v>14853</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -1067,7 +1075,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1400.html</t>
+          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1600.html</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
@@ -1079,30 +1087,30 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Радиатор панельный Ventil Compact</t>
+          <t>- грунт ГФ-021</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>CV22-400-1600</t>
+          <t>ГФ-021</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 160</t>
+          <t>Грунтовка ГФ-021 (ГОСТ 25129-2020) в Москве</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>14853</v>
+        <v>155</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>nord-heat.ru</t>
+          <t>www.russcvet.ru</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1600.html</t>
+          <t>https://www.russcvet.ru/catalog/primers/gruntovka-gf-021-gost-25129-82/</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
@@ -1114,108 +1122,108 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>- грунт ГФ-021</t>
+          <t>- краска ПФ-115 Гильзы из труб стальных водогазопроводных Ø25х3,2 Ø32x3,2 Ø40x3,5 Гильзы…</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>ГФ-021</t>
+          <t>ПФ-115</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Грунтовка ГФ-021 (ГОСТ 25129-2020) в Москве</t>
+          <t>Эмаль ПФ-115 цветная (ГОСТ 6465-76) в Красноярске</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>www.russcvet.ru</t>
+          <t>krasnoyarsk.russcvet.ru</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>https://www.russcvet.ru/catalog/primers/gruntovka-gf-021-gost-25129-82/</t>
+          <t>https://krasnoyarsk.russcvet.ru/catalog/enamels/emal-pf-115-gost-6465-76/</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>- краска ПФ-115 Гильзы из труб стальных водогазопроводных Ø25х3,2 Ø32x3,2 Ø40x3,5 Гильзы…</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>ПФ-115</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Эмаль ПФ-115 серая Россия ГОСТ 6465-76 20 кг</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>www.dizar.ru</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>https://www.dizar.ru/product/emal-pf-115-seraya-gost-6465-76-20-kg/</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Огнезащитная изоляция</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>МБФ 5</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Огнезащита МБФ-5 (EI 30, EI 45)</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>12411</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>komplektovik.ru</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>http://komplektovik.ru/vse-dlya-montaja/krepejnie-materialy/teploizoljacija-ognezashita-vozduhovodov-v-tolyatti/ognezaxhita-mbf-5-tolyatti-samara-kupit/</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>⚠ цена, похоже, за рулон, в позиции м² (104 м²)</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Огнезащитная изоляция</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>МБФ 5</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Огнезащита МБФ-5 (EI 30, EI 45)</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>12411</v>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>komplektovik.ru</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>http://komplektovik.ru/vse-dlya-montaja/krepejnie-materialy/teploizoljacija-ognezashita-vozduhovodov-v-tolyatti/ognezaxhita-mbf-5-tolyatti-samara-kupit/</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>⚠ цена, похоже, за рулон, в позиции м² (104 м²)</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Вентилятор осевой вытяжной c антимоскитной сеткой</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ERA 4</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Вентилятор осевой вытяжной ERA 4 D100</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1268</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>vent48.ru</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>https://vent48.ru/magazin/product/ventilyator-osevoy-vytyazhnoy-c-antimoskitnoy-setkoy-era-4s-d100</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1223,69 +1231,73 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Вентилятор осевой вытяжной c антимоскитной сеткой</t>
+          <t>Решетка регулируемая</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>ERA 4</t>
+          <t>АМР 600х400</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Вентилятор осевой вытяжной ERA 4 D100</t>
+          <t>Решётка Арктос АМР 600х400</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1268</v>
+        <v>4091</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>vent48.ru</t>
+          <t>ads-climate.ru</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>https://vent48.ru/magazin/product/ventilyator-osevoy-vytyazhnoy-c-antimoskitnoy-setkoy-era-4s-d100</t>
+          <t>https://ads-climate.ru/reshetki/tproduct/499828053-436272497451-reshyotka-arktos-amr-600h400</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Решетка регулируемая</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>АМР 150х150</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Однорядная решетка АМР с клапаном расхода воздуха 150х150</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>1286</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>www.vc-systems.ru</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://www.vc-systems.ru/catalog/vozduhoraspredelitelnyie_ustroystva/nastennyie_reshetki/reshetki_amr-m_385.html?sku=503</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Термометр биметаллический O80мм 0..160С, L=100 мм, кл. точн. 1.5, IP54</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>IP54</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Термометр БТ-41.211(0-160°С)G1/2.64.1,5 - ROSMA-RUSSIA</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>975</v>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>rosma-russia.ru</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>https://rosma-russia.ru/shop/termometry/termometry-obshhetehnicheskie-osevoe-prisoedinenie/termometr-bt-41-2110-160sg1-2-64-15/</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>⚠ L=100 мм в позиции, L=64 мм на карточке (Ø80 и 0-160 совпал…</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1293,30 +1305,30 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Решетка регулируемая</t>
+          <t>Манометр показывающий ТМ510 0..16бар. O100мм. G1/2. кл. точн. 1.5. IP54</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>АМР 600х400</t>
+          <t>ТМ510</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Решётка Арктос АМР 600х400</t>
+          <t xml:space="preserve">Манометр Росма ТМ-510Р.00 (0-1.6 МПа) G1/2 М2 общетехнический 100 мм, </t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4091</v>
+        <v>654</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>ads-climate.ru</t>
+          <t>dn.ru</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>https://ads-climate.ru/reshetki/tproduct/499828053-436272497451-reshyotka-arktos-amr-600h400</t>
+          <t>https://dn.ru/kipia/manometry/radialnyi/rosma/tm510r-m2/1.6mpa</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr"/>
@@ -1328,35 +1340,35 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Термометр биметаллический O80мм 0..160С, L=100 мм, кл. точн. 1.5, IP54</t>
+          <t>Шкаф учета с тепловычислителем ТВ7-04М(RS232)</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>IP54</t>
+          <t>ТВ7-04М</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Термометр БТ-41.211(0-160°С)G1/2.64.1,5 - ROSMA-RUSSIA</t>
+          <t>Тепловычислитель ТВ7-04М, Термотроник</t>
         </is>
       </c>
       <c r="E27" s="10" t="n">
-        <v>975</v>
+        <v>37900</v>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>rosma-russia.ru</t>
+          <t>energymeter.su</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>https://rosma-russia.ru/shop/termometry/termometry-obshhetehnicheskie-osevoe-prisoedinenie/termometr-bt-41-2110-160sg1-2-64-15/</t>
+          <t>https://energymeter.su/product/teplovychislitel-tv7-04m-bp-termotronik/</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>⚠ L=100 мм в позиции, L=64 мм на карточке (Ø80 и 0-160 совпал…</t>
+          <t>⚠ в позиции шкаф учёта, на карточке только тепловычислитель</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr"/>
@@ -1367,73 +1379,69 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Манометр показывающий ТМ510 0..16бар. O100мм. G1/2. кл. точн. 1.5. IP54</t>
+          <t>Расходомер Питерфлоу Dy40/Фланцевый/Qmax 22/Tmax150/PN16 тип РС 40-22-А-Ф1</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>ТМ510</t>
+          <t>А-Ф1</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Манометр Росма ТМ-510Р.00 (0-1.6 МПа) G1/2 М2 общетехнический 100 мм, </t>
+          <t>Электромагнитный расходомер Питерфлоу РС40-22-А-Ф1, DN 40 PN 16, Т=0,1</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>654</v>
+        <v>94085</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>dn.ru</t>
+          <t>kromex.su</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>https://dn.ru/kipia/manometry/radialnyi/rosma/tm510r-m2/1.6mpa</t>
+          <t>https://kromex.su/product/elektromagnitnyy-raskhodomer-piterflou-rs40-22-a-f1-dn-40-pn-16-t-0-1-150-s-22-m3-ch-vkl-bp-ridan-18/</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Шкаф учета с тепловычислителем ТВ7-04М(RS232)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>ТВ7-04М</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Тепловычислитель ТВ7-04М, Термотроник</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>36580</v>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Термометр сопротивления КТС-Б-Рт100-В-х4-П-3-80/6-50-Е</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>П-3-80/6-50-Е</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>КТС-Б-Pt100-В-x4-П-3-80/6-50-Е комплект термометров с гильз. и боб</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2713</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>kipkatalog.ru</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>https://kipkatalog.ru/product/teplovychislitel-tv-7-04m-batareya-tip-aa-s-blokom-setevogo-pitaniya/</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>⚠ в позиции шкаф учёта, на карточке только тепловычислитель Т…</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>https://kipkatalog.ru/product/kts-b-pt100-v-x4-p-3-80-6-50-e-komplekt-termometrov-s-gilz-i-bob/</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1441,30 +1449,30 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Термометр сопротивления КТС-Б-Рт100-В-х4-П-3-80/6-50-Е</t>
+          <t>Регулятор перепада давлений VFG-2R/Dy32/Kvs16/Tmax150/Pmax16 сталь ф/ф</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>П-3-80/6-50-Е</t>
+          <t>VFG 2</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>КТС-Б-Pt100-В-x4-П-3-80/6-50-Е комплект термометров с гильз. и боб</t>
+          <t>Ридан VFG-2R 065B2391R — Универсальный регулирующий клапан DN32, Kvs 1</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2713</v>
+        <v>93617</v>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>kipkatalog.ru</t>
+          <t>vtp-inz.ru</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>https://kipkatalog.ru/product/kts-b-pt100-v-x4-p-3-80-6-50-e-komplekt-termometrov-s-gilz-i-bob/</t>
+          <t>https://vtp-inz.ru/catalog/teplovaya_avtomatika/regulyatory_temperatury_i_davleniya_pryamogo_deystviya/reguliruyushchie_klapany_dlya_regulyatorov_davleniya_perepada_davleniya_raskhoda_i_temperatury_bolsh/472235/</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
@@ -1476,30 +1484,30 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Регулятор перепада давлений VFG-2R/Dy32/Kvs16/Tmax150/Pmax16 сталь ф/ф</t>
+          <t>Регулирующий клапан VFM-2R/Dy25/Kvs10/Tmax150/Pmax25 чугун ф/ф</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>VFG 2</t>
+          <t>VFM 2</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Ридан VFG-2R 065B2391R — Универсальный регулирующий клапан DN32, Kvs 1</t>
+          <t>Клапан регулирующий VFM-2R DN25, Kvs 10, PN25, Ридан 065B3058R</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>93617</v>
+        <v>38383</v>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>vtp-inz.ru</t>
+          <t>kipkatalog.ru</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>https://vtp-inz.ru/catalog/teplovaya_avtomatika/regulyatory_temperatury_i_davleniya_pryamogo_deystviya/reguliruyushchie_klapany_dlya_regulyatorov_davleniya_perepada_davleniya_raskhoda_i_temperatury_bolsh/472235/</t>
+          <t>https://kipkatalog.ru/product/klapan-reguliruyuschiy-vfm-2r-dn25-kvs-10-pn25-ridan-065b3058r/</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
@@ -1511,30 +1519,30 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Регулирующий клапан VFM-2R/Dy25/Kvs10/Tmax150/Pmax25 чугун ф/ф</t>
+          <t>Электропривод ARV-1000R , 230V, импульсное управление</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>VFM 2</t>
+          <t>ARV 1000</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Клапан регулирующий VFM-2R DN25, Kvs 10, PN25, Ридан 065B3058R</t>
+          <t>Электропривод 3 х позиционный ARV-1000R 230 В</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>38383</v>
+        <v>57092</v>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>kipkatalog.ru</t>
+          <t>promobr.ru</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>https://kipkatalog.ru/product/klapan-reguliruyuschiy-vfm-2r-dn25-kvs-10-pn25-ridan-065b3058r/</t>
+          <t>https://promobr.ru/catalog/elektroprivod-3-kh-pozitsionnyy-arv-1000r-230-v/</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
@@ -1546,30 +1554,30 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Электропривод ARV-1000R , 230V, импульсное управление</t>
+          <t>Термометр биметаллический O80мм 0..160С, L=64 мм, кл. точн. 1.5, IP54</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>ARV 1000</t>
+          <t>IP54</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Электропривод 3 х позиционный ARV-1000R 230 В</t>
+          <t>Термометр БТ-41.211(0-160°С)G1/2.64.1,5 - ROSMA-RUSSIA</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>57092</v>
+        <v>975</v>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>promobr.ru</t>
+          <t>rosma-russia.ru</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>https://promobr.ru/catalog/elektroprivod-3-kh-pozitsionnyy-arv-1000r-230-v/</t>
+          <t>https://rosma-russia.ru/shop/termometry/termometry-obshhetehnicheskie-osevoe-prisoedinenie/termometr-bt-41-2110-160sg1-2-64-15/</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
@@ -1581,30 +1589,30 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Термометр биметаллический O80мм 0..160С, L=64 мм, кл. точн. 1.5, IP54</t>
+          <t>Манометр показывающий ТМ510 0..10бар. O100мм. G1/2. кл. точн. 1.5. IP54 БТП Ридан N080825…</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>IP54</t>
+          <t>ТМ510</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Термометр БТ-41.211(0-160°С)G1/2.64.1,5 - ROSMA-RUSSIA</t>
+          <t xml:space="preserve">Манометр радиальный Росма ТМ-510P.00(0-1,0MРа)G1/2.1,5.M2 100мм (0-10 </t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>975</v>
+        <v>932</v>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>rosma-russia.ru</t>
+          <t>prootoplenie.ru</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>https://rosma-russia.ru/shop/termometry/termometry-obshhetehnicheskie-osevoe-prisoedinenie/termometr-bt-41-2110-160sg1-2-64-15/</t>
+          <t>https://prootoplenie.ru/catalog/manometry/manometr-radialnyy-rosma-tm-510p-00-0-1-0mra-g1-2-1-5-m2-100mm-0-10-bar-seryy/</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr"/>
@@ -1616,182 +1624,182 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Манометр показывающий ТМ510 0..10бар. O100мм. G1/2. кл. точн. 1.5. IP54 БТП Ридан N080825…</t>
+          <t>Термометр биметаллический O80мм 0..120С, L=64 мм. кл. точн. 1.5. IP54</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>ТМ510</t>
+          <t>IP54</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Манометр радиальный Росма ТМ-510P.00(0-1,0MРа)G1/2.1,5.M2 100мм (0-10 </t>
+          <t xml:space="preserve">Термометр осевой ПРОМА ТБ80 до 120°С биметаллический, диаметр корпуса </t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>932</v>
+        <v>1038</v>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>prootoplenie.ru</t>
+          <t>dn.ru</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>https://prootoplenie.ru/catalog/manometry/manometr-radialnyy-rosma-tm-510p-00-0-1-0mra-g1-2-1-5-m2-100mm-0-10-bar-seryy/</t>
+          <t>https://dn.ru/kipia/termometry/osevoi/promo/tb-80/l-64-t-120</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Термометр биметаллический O80мм 0..120С, L=64 мм. кл. точн. 1.5. IP54</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>IP54</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Термометр осевой ПРОМА ТБ80 до 120°С биметаллический, диаметр корпуса </t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="n">
-        <v>1038</v>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>dn.ru</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>https://dn.ru/kipia/termometry/osevoi/promo/tb-80/l-64-t-120</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Моноблок НН-14</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>НН-14</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Разборный теплообменник Ридан НН-14</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>31517</v>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>teploobmen.ru</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>https://teploobmen.ru/catalog/teploobmenniki/teploobmenniki_ridan_nn/4275/</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>⚠ в позиции моноблок, на карточке разборный НН-14 без числа п…</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="n">
+      <c r="A37" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Моноблок НН-14</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>НН-14</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Разборный теплообменник Ридан НН-14</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>31517</v>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>teploobmen.ru</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>https://teploobmen.ru/catalog/teploobmenniki/teploobmenniki_ridan_nn/4275/</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>⚠ в позиции моноблок, на карточке разборный НН-14 без числа п…</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Насос RWS 25-80S</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>RWS 25-80</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Насос циркуляционный Ридан RWS 25-80S (1х220В; 0,25кВт), с гайками</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>11694</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>ruexpans.ru</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>https://ruexpans.ru/product/nasos-tsirkulyatsionnyj-ridan-rws-25-80s-1h220v-0-25kvt-s-gajkami/</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Насос RWS 25-80S</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>RWS 25-80</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Насос циркуляционный Ридан RWS 25-80S (1х220В; 0,25кВт), с гайками</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="n">
-        <v>11694</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>ruexpans.ru</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>https://ruexpans.ru/product/nasos-tsirkulyatsionnyj-ridan-rws-25-80s-1h220v-0-25kvt-s-gajkami/</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr"/>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Преобразователь давления MBS1700R. 4-20 мА/0-10 бар</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>MBS 1700</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Датчик давления Danfoss MBS 1700 (0-10 бар) 4-20 мА, G 1/2  (060G6105)</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>7716</v>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>rosarmatorg.ru</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>https://rosarmatorg.ru/datchik-davleniya-danfoss-mbs-1700-0-10-bar-4-20-ma-g-12-060g6105-463668</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>⚠ MBS1700R (Ридан) в позиции, Danfoss MBS 1700 060G6105 на ка…</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="8" t="n">
+      <c r="A39" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Преобразователь давления MBS1700R. 4-20 мА/0-10 бар</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>MBS 1700</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>Датчик давления Danfoss MBS 1700 (0-10 бар) 4-20 мА, G 1/2  (060G6105)</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>7716</v>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Регулирующий клапан VFM-2R/Dy32/Kvs16/Tmax150/Pmax25 чугун ф/ф</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>VFM 2</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Клапан регулирующий VFM-2R Ру 25 Ду 32 Kvs=16 065B3059R Ридан</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>49080</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>rosarmatorg.ru</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
-        <is>
-          <t>https://rosarmatorg.ru/datchik-davleniya-danfoss-mbs-1700-0-10-bar-4-20-ma-g-12-060g6105-463668</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>⚠ MBS1700R (Ридан) в позиции, Danfoss MBS 1700 060G6105 на ка…</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>https://rosarmatorg.ru/klapan-reguliruyuschij-vfm-2r-pn25-32-16-065b3059r-ridan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -1799,108 +1807,108 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Регулирующий клапан VFM-2R/Dy32/Kvs16/Tmax150/Pmax25 чугун ф/ф</t>
+          <t>Манометр показывающий ТМ510 0..10бар. O100мм. G1/2. кл. точн. 1.5. IP54</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>VFM 2</t>
+          <t>ТМ510</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Клапан регулирующий VFM-2R Ру 25 Ду 32 Kvs=16 065B3059R Ридан</t>
+          <t xml:space="preserve">Манометр радиальный Росма ТМ-510P.00(0-1,0MРа)G1/2.1,5.M2 100мм (0-10 </t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>49080</v>
+        <v>932</v>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>rosarmatorg.ru</t>
+          <t>prootoplenie.ru</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>https://rosarmatorg.ru/klapan-reguliruyuschij-vfm-2r-pn25-32-16-065b3059r-ridan</t>
+          <t>https://prootoplenie.ru/catalog/manometry/manometr-radialnyy-rosma-tm-510p-00-0-1-0mra-g1-2-1-5-m2-100mm-0-10-bar-seryy/</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Манометр показывающий ТМ510 0..10бар. O100мм. G1/2. кл. точн. 1.5. IP54</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>ТМ510</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Манометр радиальный Росма ТМ-510P.00(0-1,0MРа)G1/2.1,5.M2 100мм (0-10 </t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="n">
-        <v>932</v>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>prootoplenie.ru</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>https://prootoplenie.ru/catalog/manometry/manometr-radialnyy-rosma-tm-510p-00-0-1-0mra-g1-2-1-5-m2-100mm-0-10-bar-seryy/</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Термометр биметаллический O80мм 0..120С, L=100 мм, кл. точн. 1.5, IP54</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>IP54</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Общепромышленные биметаллические термометры ТБф-120 d.100</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>870</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>www.fiztech.ru</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fiztech.ru/catalog/termometry/537/</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>⚠ в позиции корпус Ø80, на карточке d.100</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Термометр биметаллический O80мм 0..120С, L=100 мм, кл. точн. 1.5, IP54</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>IP54</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>Общепромышленные биметаллические термометры ТБф-120 d.100</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>870</v>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>www.fiztech.ru</t>
-        </is>
-      </c>
-      <c r="G42" s="11" t="inlineStr">
-        <is>
-          <t>https://www.fiztech.ru/catalog/termometry/537/</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>⚠ в позиции корпус Ø80, на карточке d.100</t>
-        </is>
-      </c>
-      <c r="I42" s="8" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Насос RWS 65-120FT</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>RWS 65-120</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Насос циркуляционный RWS 65-120FT, 015P1027, Ридан</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>71135</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>kipkatalog.ru</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>https://kipkatalog.ru/product/nasos-tsirkulyatsionnyy-rws-65-120ft-015p1027-ridan/</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1908,30 +1916,30 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Насос RWS 65-120FT</t>
+          <t>Соленоидный клапан EV220WR/Dy25/Kvs10.2/Tmax130 латунь р/р</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>RWS 65-120</t>
+          <t>EV220WR</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Насос циркуляционный RWS 65-120FT, 015P1027, Ридан</t>
+          <t>Соленоидный клапан Ридан EV220WR с катушкой, уплотнение EPDM (нормальн</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>71135</v>
+        <v>13651</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>kipkatalog.ru</t>
+          <t>rtreid.ru</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>https://kipkatalog.ru/product/nasos-tsirkulyatsionnyy-rws-65-120ft-015p1027-ridan/</t>
+          <t>https://rtreid.ru/catalog/solenoidnyy-klapan-ridan-ev220wr-s-katushkoy-uplotnenie-epdm-normalno-zakrytyy-230v-du25-kvs10-2/</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
@@ -1943,30 +1951,30 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Соленоидный клапан EV220WR/Dy25/Kvs10.2/Tmax130 латунь р/р</t>
+          <t>Прессостат KPI 35R, диап. настр. давл. -0,2-7,5 бар, PN17, Tmax=120°C, G1/2", IP44</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>EV220WR</t>
+          <t>KPI 35</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Ридан 042U002531R — Клапан электромагнитный EV220WR, присоединение G1,</t>
+          <t>Реле давления KPI 35R, диапазон настройки -0,2...7,5 бар, дифференциал</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>11376</v>
+        <v>5617</v>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>ridan.ru</t>
+          <t>www.etm.ru</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>https://ridan.ru/product/042U002531R</t>
+          <t>https://www.etm.ru/cat/nn/9429140</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr"/>
@@ -1978,30 +1986,30 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Прессостат KPI 35R, диап. настр. давл. -0,2-7,5 бар, PN17, Tmax=120°C, G1/2", IP44</t>
+          <t>Датчик температуры наружный MBT 3380R, Pt1000, T=-50...+95°C, IP54</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>KPI 35</t>
+          <t>MBT 3380</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Реле давления KPI 35R, диапазон настройки -0,2...7,5 бар, дифференциал</t>
+          <t>097U1115R Датчик температуры наружного воздуха MBT3380R,  с эл.разъемо</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>5617</v>
+        <v>1307</v>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>www.etm.ru</t>
+          <t>effv.ru</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>https://www.etm.ru/cat/nn/9429140</t>
+          <t>https://effv.ru/catalog/pribory_dlya_izmereniya_i_kontrolya/datchiki_temperatury_i_vlazhnosti/ulichnye_datchiki/097u1115r_datchik_temperatury_naruzhnogo_vozdukha_mbt3380r_s_el_razemom_klass_zashchity_ip65_pt1000_/</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr"/>
@@ -2013,30 +2021,30 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Датчик температуры наружный MBT 3380R, Pt1000, T=-50...+95°C, IP54</t>
+          <t>Манометр ТМ510, 0..10бар, 100мм, G1/2</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>MBT 3380</t>
+          <t>ТМ510</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>097U1115R Датчик температуры наружного воздуха MBT3380R,  с эл.разъемо</t>
+          <t>Манометр М2 радиальный ТМ-510Р.00 0...1.0 МРа 1/2' кл.1.5., цвет-</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1307</v>
+        <v>622</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>effv.ru</t>
+          <t>www.etm.ru</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>https://effv.ru/catalog/pribory_dlya_izmereniya_i_kontrolya/datchiki_temperatury_i_vlazhnosti/ulichnye_datchiki/097u1115r_datchik_temperatury_naruzhnogo_vozdukha_mbt3380r_s_el_razemom_klass_zashchity_ip65_pt1000_/</t>
+          <t>https://www.etm.ru/cat/nn/8289418</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
@@ -2048,74 +2056,51 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Манометр ТМ510, 0..10бар, 100мм, G1/2</t>
+          <t>Балансировочный клапан MNF-R2/Dy80/Kvs122.3/Py25/TMax150 ф/ф</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>ТМ510</t>
+          <t>MNF-R2</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Манометр М2 радиальный ТМ-510Р.00 0...1.0 МРа 1/2' кл.1.5., цвет-</t>
+          <t xml:space="preserve">003Z1072R MNF-R2 DN80 ручной балансировочный клапан, фланцевый, PN25, </t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>622</v>
+        <v>66011</v>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>www.etm.ru</t>
+          <t>teploingsnab.ru</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>https://www.etm.ru/cat/nn/8289418</t>
+          <t>https://teploingsnab.ru/003z1072r-mnf-r2-dn80-ruchnoy-balansirovochnyy-klapan-flantsevyy-pn25-tmax-150c/</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Балансировочный клапан MNF-R2/Dy80/Kvs122.3/Py25/TMax150 ф/ф</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>MNF-R2</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">003Z1072R MNF-R2 DN80 ручной балансировочный клапан, фланцевый, PN25, </t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n">
-        <v>66011</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>teploingsnab.ru</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>https://teploingsnab.ru/003z1072r-mnf-r2-dn80-ruchnoy-balansirovochnyy-klapan-flantsevyy-pn25-tmax-150c/</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="4" t="inlineStr"/>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Искали, но цену не нашли:</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Искали, но цену не нашли:</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Радиатор панельный Ventil Compact</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CV22-400-900</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2167,12 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>Расходомер Питерфлоу Dy40/Фланцевый/Qmax 22/Tmax150/PN16 тип РС 40-22-А-Ф1</t>
+          <t>Решетка регулируемая</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>А-Ф1</t>
+          <t>АМР 150х150</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2261,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
+++ b/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
@@ -1444,39 +1444,43 @@
       <c r="I29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Регулятор перепада давлений VFG-2R/Dy32/Kvs16/Tmax150/Pmax16 сталь ф/ф</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>VFG 2</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Ридан VFG-2R 065B2391R — Универсальный регулирующий клапан DN32, Kvs 1</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="10" t="n">
         <v>93617</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>vtp-inz.ru</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>https://vtp-inz.ru/catalog/teplovaya_avtomatika/regulyatory_temperatury_i_davleniya_pryamogo_deystviya/reguliruyushchie_klapany_dlya_regulyatorov_davleniya_perepada_davleniya_raskhoda_i_temperatury_bolsh/472235/</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>⚠ в позиции Kvs 16, на карточке написано Kvs 1 (артикул и Ду32 совпали)</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2363,20 +2367,20 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Клапан обратный осевой латунь CA1103 Ду 25 Ру16 ВР G1" Tecofi CA1103-0</t>
+          <t>Клапан обратный латунь CA1103 Ду 25 Ру16 ВР/ВР Tecofi CA1103-0025</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>980</v>
+        <v>513</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>snabteploservis.ru</t>
+          <t>stroy-mart.ru</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://snabteploservis.ru/klapan-obratnyj-osevoj-latun-ca1103-du-25-ru16-vr-g1-tecofi-ca1103-0025/</t>
+          <t>https://stroy-mart.ru/product/klapan-obratnyy-latun-ca1103-du-25-ru16-vrvr-tecofi-ca1103-0025/</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -2398,20 +2402,20 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Обратный клапан Tecofi 1/2` bp пружинный муфтовый | CA1103-0015 латунн</t>
+          <t>Клапан обратный латунь CA1103 Ду 15 Ру16 ВР/ВР Tecofi CA1103-0015</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>740</v>
+        <v>256</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>feniks-trade.ru</t>
+          <t>stroy-mart.ru</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>https://feniks-trade.ru/obratnye-klapany-tecofi/tecofi-ca1103-0015</t>
+          <t>https://stroy-mart.ru/product/klapan-obratnyy-latun-ca1103-du-15-ru16-vrvr-tecofi-ca1103-0015/</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
@@ -2573,20 +2577,20 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Осевой муфтовый обратный клапан, ДУ 2“</t>
+          <t>Клапан обратный латунь CA1103 Ду 50 Ру16 ВР/ВР Tecofi CA1103-0050</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2794</v>
+        <v>2049</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>astra-pools.com</t>
+          <t>stroy-mart.ru</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://astra-pools.com/zapornaya-armatura-tecofi/obratnye-klapany/osevoy-muftovyy-obratnyy-klapan-du-2-69</t>
+          <t>https://stroy-mart.ru/product/klapan-obratnyy-latun-ca1103-du-50-ru16-vrvr-tecofi-ca1103-0050/</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr"/>
@@ -2663,39 +2667,43 @@
       <c r="I13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Манометр ТМ серия 10 модель 2</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>ТМ-510P.00</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>РОСМА  ТМ-510P.00(0-1,6MРа)G1/2.1,5.M2  Манометр диам. 100 мм; тип ТМ;</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="10" t="n">
         <v>353</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>suntehnik.ru</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>https://suntehnik.ru/catalog/manometry/rosma_tm_510p_00_0_1_6mra_g1_2_1_5_m2_manometr_diam_100_mm_tip_tm_seriya_10_model_2_kt_1_5_ip40_g1_2/</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>⚠ в позиции предел 0–0,4 МПа и резьба М20×1,5, на карточке 0–1,6 МПа и G1/2</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">

--- a/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
+++ b/docs/meetings/2026-09-11_Иван_проверка-цен/Проверка_цен_Арта_Ласточка.xlsx
@@ -83,6 +83,18 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -93,18 +105,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -580,1514 +580,1518 @@
           <t>https://dn.ru/kipia/teploschetchik/ultrazvukovoy/danfoss/sonoselect10-kv-podacha/dn15-0-6m</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>⚠ в позиции qp=1,5 м³/ч, на карточке 0,6 м³/ч — проверено на странице 12.09</t>
+        </is>
+      </c>
       <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Compact</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>C22-400-600</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Compact (тип 22 высота 400 мм длина 600 мм) бо</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="10" t="n">
         <v>5831</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/compact/c22-400-600.html</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Compact</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>C22-400-1200</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Compact (тип 22 высота 400 мм длина 1200 мм) б</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="10" t="n">
         <v>10119</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/compact/c22-400-1200.html</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Радиатор панельный Compact</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>C22-400-1400</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Радиатор стальной панельный 22/400/1400 боковое подключение</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="6" t="n">
         <v>42159</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>www.etm.ru</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>https://www.etm.ru/cat/nn/8158067</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>⚠ бренд не указан, цена в ~4 раза выше прошлой находки</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Радиатор панельный Compact</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>C33-400-1000</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Радиатор стальной панельный 33/400/1000 боковое подключение</t>
         </is>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="6" t="n">
         <v>45857</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>www.etm.ru</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>https://www.etm.ru/cat/nn/2168747</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>⚠ бренд не указан, цена в ~2 раза выше прошлой находки</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>CV11-400-1000</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 11 высота 400 мм длина 100</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="10" t="n">
         <v>6979</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv11-400-1000.html</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>CV11-400-1200</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Радиатор сталь панельный EVRA Ventil Compact 11CV 400x1200</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="10" t="n">
         <v>6153</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>stoking.ru</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>https://stoking.ru/products/radiator-stal-panelnyy-evra-ventil-compact-11cv-400x1200</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>CV11-400-1400</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 11 высота 400 мм длина 140</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="10" t="n">
         <v>8555</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv11-400-1400.html</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>CV11-400-1600</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Радиатор сталь панельный EVRA Ventil Compact 11CV 400x1600</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="10" t="n">
         <v>8216</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>profsnabeng.ru</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>https://profsnabeng.ru/product/109471-evra-cv-11-400-1600-evra_r</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>CV22-400-700</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 700</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="10" t="n">
         <v>8335</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-700.html</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>CV22-400-800</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 800</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="10" t="n">
         <v>9005</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-800.html</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>CV22-400-1000</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 100</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="10" t="n">
         <v>10598</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1000.html</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>CV22-400-1200</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 120</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="10" t="n">
         <v>11953</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1200.html</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>CV22-400-1400</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 140</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="10" t="n">
         <v>13277</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1400.html</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Радиатор панельный Ventil Compact</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>CV22-400-1600</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Панельный радиатор Evra Ventil Compact (тип 22 высота 400 мм длина 160</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="10" t="n">
         <v>14853</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>nord-heat.ru</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>https://nord-heat.ru/steel/ventil-compact/cv22-400-1600.html</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>- грунт ГФ-021</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>ГФ-021</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Грунтовка ГФ-021 (ГОСТ 25129-2020) в Москве</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="10" t="n">
         <v>155</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>www.russcvet.ru</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>https://www.russcvet.ru/catalog/primers/gruntovka-gf-021-gost-25129-82/</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>- краска ПФ-115 Гильзы из труб стальных водогазопроводных Ø25х3,2 Ø32x3,2 Ø40x3,5 Гильзы…</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>ПФ-115</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Эмаль ПФ-115 цветная (ГОСТ 6465-76) в Красноярске</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="10" t="n">
         <v>165</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>krasnoyarsk.russcvet.ru</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>https://krasnoyarsk.russcvet.ru/catalog/enamels/emal-pf-115-gost-6465-76/</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Огнезащитная изоляция</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>МБФ 5</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Огнезащита МБФ-5 (EI 30, EI 45)</t>
         </is>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="6" t="n">
         <v>12411</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>komplektovik.ru</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>http://komplektovik.ru/vse-dlya-montaja/krepejnie-materialy/teploizoljacija-ognezashita-vozduhovodov-v-tolyatti/ognezaxhita-mbf-5-tolyatti-samara-kupit/</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>⚠ цена, похоже, за рулон, в позиции м² (104 м²)</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Вентилятор осевой вытяжной c антимоскитной сеткой</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>ERA 4</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Вентилятор осевой вытяжной ERA 4 D100</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="10" t="n">
         <v>1268</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>vent48.ru</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>https://vent48.ru/magazin/product/ventilyator-osevoy-vytyazhnoy-c-antimoskitnoy-setkoy-era-4s-d100</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Решетка регулируемая</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>АМР 600х400</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Решётка Арктос АМР 600х400</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="10" t="n">
         <v>4091</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>ads-climate.ru</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>https://ads-climate.ru/reshetki/tproduct/499828053-436272497451-reshyotka-arktos-amr-600h400</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="4" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Термометр биметаллический O80мм 0..160С, L=100 мм, кл. точн. 1.5, IP54</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>IP54</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Термометр БТ-41.211(0-160°С)G1/2.64.1,5 - ROSMA-RUSSIA</t>
         </is>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="6" t="n">
         <v>975</v>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>rosma-russia.ru</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>https://rosma-russia.ru/shop/termometry/termometry-obshhetehnicheskie-osevoe-prisoedinenie/termometr-bt-41-2110-160sg1-2-64-15/</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>⚠ L=100 мм в позиции, L=64 мм на карточке (Ø80 и 0-160 совпал…</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Манометр показывающий ТМ510 0..16бар. O100мм. G1/2. кл. точн. 1.5. IP54</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>ТМ510</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Манометр Росма ТМ-510Р.00 (0-1.6 МПа) G1/2 М2 общетехнический 100 мм, </t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="10" t="n">
         <v>654</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>dn.ru</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>https://dn.ru/kipia/manometry/radialnyi/rosma/tm510r-m2/1.6mpa</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Шкаф учета с тепловычислителем ТВ7-04М(RS232)</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>ТВ7-04М</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Тепловычислитель ТВ7-04М, Термотроник</t>
         </is>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="6" t="n">
         <v>37900</v>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>energymeter.su</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>https://energymeter.su/product/teplovychislitel-tv7-04m-bp-termotronik/</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>⚠ в позиции шкаф учёта, на карточке только тепловычислитель</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Расходомер Питерфлоу Dy40/Фланцевый/Qmax 22/Tmax150/PN16 тип РС 40-22-А-Ф1</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>А-Ф1</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Электромагнитный расходомер Питерфлоу РС40-22-А-Ф1, DN 40 PN 16, Т=0,1</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="10" t="n">
         <v>94085</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>kromex.su</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>https://kromex.su/product/elektromagnitnyy-raskhodomer-piterflou-rs40-22-a-f1-dn-40-pn-16-t-0-1-150-s-22-m3-ch-vkl-bp-ridan-18/</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="4" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Термометр сопротивления КТС-Б-Рт100-В-х4-П-3-80/6-50-Е</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>П-3-80/6-50-Е</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>КТС-Б-Pt100-В-x4-П-3-80/6-50-Е комплект термометров с гильз. и боб</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="10" t="n">
         <v>2713</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>kipkatalog.ru</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>https://kipkatalog.ru/product/kts-b-pt100-v-x4-p-3-80-6-50-e-komplekt-termometrov-s-gilz-i-bob/</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Регулятор перепада давлений VFG-2R/Dy32/Kvs16/Tmax150/Pmax16 сталь ф/ф</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>VFG 2</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Ридан VFG-2R 065B2391R — Универсальный регулирующий клапан DN32, Kvs 1</t>
         </is>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="6" t="n">
         <v>93617</v>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>vtp-inz.ru</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>https://vtp-inz.ru/catalog/teplovaya_avtomatika/regulyatory_temperatury_i_davleniya_pryamogo_deystviya/reguliruyushchie_klapany_dlya_regulyatorov_davleniya_perepada_davleniya_raskhoda_i_temperatury_bolsh/472235/</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>⚠ в позиции Kvs 16, на карточке написано Kvs 1 (артикул и Ду32 совпали)</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Регулирующий клапан VFM-2R/Dy25/Kvs10/Tmax150/Pmax25 чугун ф/ф</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>VFM 2</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Клапан регулирующий VFM-2R DN25, Kvs 10, PN25, Ридан 065B3058R</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="10" t="n">
         <v>38383</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>kipkatalog.ru</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>https://kipkatalog.ru/product/klapan-reguliruyuschiy-vfm-2r-dn25-kvs-10-pn25-ridan-065b3058r/</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Электропривод ARV-1000R , 230V, импульсное управление</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>ARV 1000</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Электропривод 3 х позиционный ARV-1000R 230 В</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="10" t="n">
         <v>57092</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>promobr.ru</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>https://promobr.ru/catalog/elektroprivod-3-kh-pozitsionnyy-arv-1000r-230-v/</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="4" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Термометр биметаллический O80мм 0..160С, L=64 мм, кл. точн. 1.5, IP54</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>IP54</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Термометр БТ-41.211(0-160°С)G1/2.64.1,5 - ROSMA-RUSSIA</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="10" t="n">
         <v>975</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>rosma-russia.ru</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>https://rosma-russia.ru/shop/termometry/termometry-obshhetehnicheskie-osevoe-prisoedinenie/termometr-bt-41-2110-160sg1-2-64-15/</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Манометр показывающий ТМ510 0..10бар. O100мм. G1/2. кл. точн. 1.5. IP54 БТП Ридан N080825…</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>ТМ510</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Манометр радиальный Росма ТМ-510P.00(0-1,0MРа)G1/2.1,5.M2 100мм (0-10 </t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="10" t="n">
         <v>932</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>prootoplenie.ru</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>https://prootoplenie.ru/catalog/manometry/manometr-radialnyy-rosma-tm-510p-00-0-1-0mra-g1-2-1-5-m2-100mm-0-10-bar-seryy/</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Термометр биметаллический O80мм 0..120С, L=64 мм. кл. точн. 1.5. IP54</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>IP54</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Термометр осевой ПРОМА ТБ80 до 120°С биметаллический, диаметр корпуса </t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="10" t="n">
         <v>1038</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>dn.ru</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>https://dn.ru/kipia/termometry/osevoi/promo/tb-80/l-64-t-120</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Моноблок НН-14</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>НН-14</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Разборный теплообменник Ридан НН-14</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="6" t="n">
         <v>31517</v>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>teploobmen.ru</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>https://teploobmen.ru/catalog/teploobmenniki/teploobmenniki_ridan_nn/4275/</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>⚠ в позиции моноблок, на карточке разборный НН-14 без числа п…</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Насос RWS 25-80S</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>RWS 25-80</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Насос циркуляционный Ридан RWS 25-80S (1х220В; 0,25кВт), с гайками</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="10" t="n">
         <v>11694</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>ruexpans.ru</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>https://ruexpans.ru/product/nasos-tsirkulyatsionnyj-ridan-rws-25-80s-1h220v-0-25kvt-s-gajkami/</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Преобразователь давления MBS1700R. 4-20 мА/0-10 бар</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>MBS 1700</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Датчик давления Danfoss MBS 1700 (0-10 бар) 4-20 мА, G 1/2  (060G6105)</t>
         </is>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="6" t="n">
         <v>7716</v>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>rosarmatorg.ru</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>https://rosarmatorg.ru/datchik-davleniya-danfoss-mbs-1700-0-10-bar-4-20-ma-g-12-060g6105-463668</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>⚠ MBS1700R (Ридан) в позиции, Danfoss MBS 1700 060G6105 на ка…</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Регулирующий клапан VFM-2R/Dy32/Kvs16/Tmax150/Pmax25 чугун ф/ф</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>VFM 2</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Клапан регулирующий VFM-2R Ру 25 Ду 32 Kvs=16 065B3059R Ридан</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="10" t="n">
         <v>49080</v>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>rosarmatorg.ru</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>https://rosarmatorg.ru/klapan-reguliruyuschij-vfm-2r-pn25-32-16-065b3059r-ridan</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Манометр показывающий ТМ510 0..10бар. O100мм. G1/2. кл. точн. 1.5. IP54</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>ТМ510</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Манометр радиальный Росма ТМ-510P.00(0-1,0MРа)G1/2.1,5.M2 100мм (0-10 </t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="10" t="n">
         <v>932</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>prootoplenie.ru</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>https://prootoplenie.ru/catalog/manometry/manometr-radialnyy-rosma-tm-510p-00-0-1-0mra-g1-2-1-5-m2-100mm-0-10-bar-seryy/</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Термометр биметаллический O80мм 0..120С, L=100 мм, кл. точн. 1.5, IP54</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>IP54</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Общепромышленные биметаллические термометры ТБф-120 d.100</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E41" s="6" t="n">
         <v>870</v>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>www.fiztech.ru</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>https://www.fiztech.ru/catalog/termometry/537/</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>⚠ в позиции корпус Ø80, на карточке d.100</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Насос RWS 65-120FT</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>RWS 65-120</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Насос циркуляционный RWS 65-120FT, 015P1027, Ридан</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="10" t="n">
         <v>71135</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>kipkatalog.ru</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>https://kipkatalog.ru/product/nasos-tsirkulyatsionnyy-rws-65-120ft-015p1027-ridan/</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="4" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Соленоидный клапан EV220WR/Dy25/Kvs10.2/Tmax130 латунь р/р</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>EV220WR</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>Соленоидный клапан Ридан EV220WR с катушкой, уплотнение EPDM (нормальн</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="10" t="n">
         <v>13651</v>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>rtreid.ru</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>https://rtreid.ru/catalog/solenoidnyy-klapan-ridan-ev220wr-s-katushkoy-uplotnenie-epdm-normalno-zakrytyy-230v-du25-kvs10-2/</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="4" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Прессостат KPI 35R, диап. настр. давл. -0,2-7,5 бар, PN17, Tmax=120°C, G1/2", IP44</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>KPI 35</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>Реле давления KPI 35R, диапазон настройки -0,2...7,5 бар, дифференциал</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="10" t="n">
         <v>5617</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>www.etm.ru</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>https://www.etm.ru/cat/nn/9429140</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="4" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Датчик температуры наружный MBT 3380R, Pt1000, T=-50...+95°C, IP54</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>MBT 3380</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>097U1115R Датчик температуры наружного воздуха MBT3380R,  с эл.разъемо</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="10" t="n">
         <v>1307</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>effv.ru</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>https://effv.ru/catalog/pribory_dlya_izmereniya_i_kontrolya/datchiki_temperatury_i_vlazhnosti/ulichnye_datchiki/097u1115r_datchik_temperatury_naruzhnogo_vozdukha_mbt3380r_s_el_razemom_klass_zashchity_ip65_pt1000_/</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="4" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Манометр ТМ510, 0..10бар, 100мм, G1/2</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>ТМ510</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>Манометр М2 радиальный ТМ-510Р.00 0...1.0 МРа 1/2' кл.1.5., цвет-</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="10" t="n">
         <v>622</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t>www.etm.ru</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>https://www.etm.ru/cat/nn/8289418</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Балансировочный клапан MNF-R2/Dy80/Kvs122.3/Py25/TMax150 ф/ф</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>MNF-R2</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">003Z1072R MNF-R2 DN80 ручной балансировочный клапан, фланцевый, PN25, </t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="10" t="n">
         <v>66011</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>teploingsnab.ru</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>https://teploingsnab.ru/003z1072r-mnf-r2-dn80-ruchnoy-balansirovochnyy-klapan-flantsevyy-pn25-tmax-150c/</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="4" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -2352,506 +2356,506 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный осевой муфтовый корпус латунь, диск нитрил G1''</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>CA1103-0025</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный латунь CA1103 Ду 25 Ру16 ВР/ВР Tecofi CA1103-0025</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="10" t="n">
         <v>513</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>stroy-mart.ru</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>https://stroy-mart.ru/product/klapan-obratnyy-latun-ca1103-du-25-ru16-vrvr-tecofi-ca1103-0025/</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный осевой муфтовый корпус латунь, диск нитрил G1/2''</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>CA1103-0015</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный латунь CA1103 Ду 15 Ру16 ВР/ВР Tecofi CA1103-0015</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="10" t="n">
         <v>256</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>stroy-mart.ru</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>https://stroy-mart.ru/product/klapan-obratnyy-latun-ca1103-du-15-ru16-vrvr-tecofi-ca1103-0015/</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный осевой фланцевый корпус чугун, диск чугун, PN16 Ду50</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>CA3241-0050</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>CA3241-0050 - Обратный клапан CA3241 Ду50 Ру16 Tecofi</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="10" t="n">
         <v>8479</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>termopartner.ru</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>https://termopartner.ru/catalog/truboprovodnaya_armatura/obratnye_klapany/obratnye_klapany_tecofi/obratnye_klapany_ca3241_tecofi/obratnyy_klapan_ca3241_0050_tecofi_du50_ru16/</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Кран шаровой латунный для природного газа 11Б27п Ду25 А12 газнр/нр рычаг</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Б27п</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Кран шаровой латунный газ 11б27п А12 Ду 25 НР рычаг БАЗ А500мм</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="10" t="n">
         <v>288</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>rosarmatorg.ru</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>https://rosarmatorg.ru/kran-sharovoj-latunnij-gaz-11b27p-a12-du-25-nr-richag-baz-a500mm-100-439-5282</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Кран шаровой латунный для природного газа 11Б27п Ду25 А12 газнр/нр рычаг</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Б27п</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Кран шаровой латунный газ 11б27п А12 Ду 25 НР рычаг БАЗ А500мм</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="10" t="n">
         <v>288</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>rosarmatorg.ru</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>https://rosarmatorg.ru/kran-sharovoj-latunnij-gaz-11b27p-a12-du-25-nr-richag-baz-a500mm-100-439-5282</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>РЕДУКТОР ДАВЛЕНИЯ ПОРШНЕВОЙ HEIZEN 304 Ду15</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>HEIZEN 304</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Редуктор давления поршневой Heizen 1/2"</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="10" t="n">
         <v>865</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>www.vestatrade.ru</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>https://www.vestatrade.ru/predohranitelno-reguliruyushchaya-armatura/reduktory-davleniya/reduktory-davleniya-heizen/reduktor-davlenija-porshnevoj-heizen-12/</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный осевой муфтовый корпус латунь, диск нитрил G2''</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>CA1103-0050</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный латунь CA1103 Ду 50 Ру16 ВР/ВР Tecofi CA1103-0050</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="10" t="n">
         <v>2049</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>stroy-mart.ru</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>https://stroy-mart.ru/product/klapan-obratnyy-latun-ca1103-du-50-ru16-vrvr-tecofi-ca1103-0050/</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Кран шаровой латунный для природного газа 11Б27п Ду50 А12 газнр/нр рычаг</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Б27п</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Кран газовый шаровый 11Б27П Ду50 ручка</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="10" t="n">
         <v>2310</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>tehnogazpribor.ru</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>https://tehnogazpribor.ru/product/kran-gazovyj-sharovyj-11b27p-du50-ruchka/</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Кран для манометра трехходовой (кран под манометр) ABRA VFM16-FGFG DN15 PN16 внутр.G1/2 /…</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>VFM 16</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>ABRA VFM16-FGFG внутр.G1/2” / внутр. G1/2”</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="10" t="n">
         <v>628</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>armarost.ru</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>https://armarost.ru/catalog/zapornaya_armatura/krany/krany_sharovye_latunnye/abra_vfm16_fgfg_vnutr_g1_2_vnutr_g1_2.html</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Манометр ТМ серия 10 модель 2</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>ТМ-510P.00</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>РОСМА  ТМ-510P.00(0-1,6MРа)G1/2.1,5.M2  Манометр диам. 100 мм; тип ТМ;</t>
         </is>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="6" t="n">
         <v>353</v>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>suntehnik.ru</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>https://suntehnik.ru/catalog/manometry/rosma_tm_510p_00_0_1_6mra_g1_2_1_5_m2_manometr_diam_100_mm_tip_tm_seriya_10_model_2_kt_1_5_ip40_g1_2/</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>⚠ в позиции предел 0–0,4 МПа и резьба М20×1,5, на карточке 0–1,6 МПа и G1/2</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Клапан обратный осевой фланцевый корпус чугун, диск чугун, PN16 Ду65</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>CA3241-0065</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>CA3241-0065 - Обратный клапан CA3241 Ду65 Ру16 Tecofi</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="10" t="n">
         <v>11986</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>termopartner.ru</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>https://termopartner.ru/catalog/truboprovodnaya_armatura/obratnye_klapany/obratnye_klapany_tecofi/obratnye_klapany_ca3241_tecofi/obratnyy_klapan_ca3241_0065_tecofi_du65_ru16/</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Воронка кровельная обогреваемая с обжимным металлическим фланцем и листвоуловителе VMO 11…</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>VMO 110x165</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Кровельная воронка Fachmann VMO 110x165 с электроподогревом, листвоуло</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="10" t="n">
         <v>6950</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>teploshop.ru</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>https://teploshop.ru/catalog/fachmann_vmo_110x165_s_elektropodogrevom.html</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="4" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Насосная повысительная установка с насосами ANTARUS 3 MLV4-6/01/GPRS производительностью…</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>ANTARUS 3</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Насосная станция Antarus 3MLV4-6</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="6" t="n">
         <v>868753</v>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>msk.tssib.ru</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>https://msk.tssib.ru/nasosnoe-oborudovanie/nasosnye-stantsii/ustanovki-povysheniya-davleniya/ustanovki-povysheniya-davleniya-antarus/nasosnaya-stantsiya-antarus-3mlv4-6/</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>⚠ модель 3MLV4-6 совпала, но на стр. 1,1 кВт/14 м3/ч/45 м про…</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Насосная повысительная установка с насосами ANTARUS 3 MLV4-7/01/GPRS производительностью…</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>ANTARUS 3</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Насосная станция Antarus 3MLV4-3</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="6" t="n">
         <v>873275</v>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>tssib.ru</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>https://tssib.ru/nasosnoe-oborudovanie/nasosnye-stantsii/ustanovki-povysheniya-davleniya/ustanovki-povysheniya-davleniya-antarus/nasosnaya-stantsiya-antarus-3mlv4-3/</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>⚠ 3MLV4-7 в позиции, 3MLV4-3 на карточке</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
